--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>assert_detail</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>similarity_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -488,7 +493,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>你好，我是DeepSeek，一个由深度求索公司创造的AI助手，致力于用热情和细心为你提供帮助！😊</t>
+          <t>你好，我是DeepSeek，一个由深度求索公司创造的AI助手，致力于用热情和细腻的方式为你提供帮助！😊</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -497,14 +502,21 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>相似度得分 0.2056，低于阈值 0.5</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.205581311334517</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,8 +534,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1 + 1 = 2。  
-这是一个基础的算术加法运算结果。</t>
+          <t>1 + 1 在基本的算术运算中等于 **2**。  
+如果你是在其他语境下提问（比如二进制、布尔代数、文字游戏等），答案可能不同，例如：  
+- 二进制：1 + 1 = 10  
+- 布尔代数：1 + 1 = 1（逻辑或运算）  
+- 脑筋急转弯：1 + 1 = 田（汉字拼接）  
+但通常来说，数学上的标准答案是 **2**。</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -532,14 +548,21 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>相似度得分 0.1504，低于阈值 0.5</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1504108195861099</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,53 +582,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>当然！选择哪本Python书主要取决于你的**基础水平**和**学习目标**。我将分门别类为你推荐几本公认的经典好书。
-### 一、 零基础入门（最适合新手）
-这类书假设你完全没有编程经验，从最基础的概念讲起。
-1.  **《Python编程：从入门到实践》（第2版） - Eric Matthes**
-    *   **推荐理由**：**全球最畅销的Python入门书**，口碑极佳。结构非常清晰，分为两部分：
-        *   **第一部分：基础知识** - 讲解核心语法概念，每章都有动手练习。
-        *   **第二部分：项目实践** - 通过开发“外星人入侵”游戏、数据可视化项目、Web应用程序三个项目，将所学知识融会贯通。
-    *   **适合人群**：绝对的新手，喜欢“学中做、做中学”的人。
-2.  **《笨办法学Python3》 - Zed A. Shaw**
-    *   **推荐理由**：强调**动手和重复**。通过52个精心设计的练习，让你强制性地打字、读代码、改代码，培养最直接的编程手感。风格比较直接，甚至有点“粗暴”，但效果显著。
-    *   **适合人群**：不喜欢太多理论，希望通过大量练习形成肌肉记忆的初学者。
-### 二、 有一定基础，想深入理解Python（进阶必读）
-当你掌握了基础语法，能写一些小程序后，这些书能让你真正理解Python的精髓，写出更高效、优雅的代码。
-1.  **《流畅的Python》 - Luciano Ramalho**
-    *   **推荐理由**：**Python进阶的圣经级作品**。它不教你基础语法，而是深入探讨Python的**数据结构、函数、面向对象、元编程等核心特性**。读完你会惊叹：“原来Python还能这么用！”
-    *   **适合人群**：已入门，想从“会写”代码提升到“写好”代码的开发者。不适合零基础。
-2.  **《Effective Python：编写高质量Python代码的90个有效方法》（第2版） - Brett Slatkin**
-    *   **推荐理由**：一本非常实用的“招式集”。它通过90条具体的规则，告诉你什么是Pythonic的写法，如何避免常见的陷阱和错误。条理清晰，每一条都很有用。
-    *   **适合人群**：希望快速提升代码质量和专业性的开发者。可以当作手册随时翻阅。
-### 三、 特定领域应用
-如果你有明确的目标，比如做数据分析、自动化办公或Web开发，可以直接选择领域内的经典书。
-1.  **数据分析/科学计算**
-    *   **《利用Python进行数据分析》（第2版） - Wes McKinney**
-        *   **推荐理由**：由Pandas库的创始人撰写，是**用Python做数据分析的绝对权威指南**。重点讲解NumPy, Pandas, Matplotlib等核心库。
-        *   **适合人群**：想做数据分析、金融量化、科学研究的读者。
-2.  **自动化与运维**
-    *   **《Python自动化编程实战：让繁琐工作自动化》 - Al Sweigart**
-        *   **推荐理由**：教你用Python自动处理Excel、PDF、邮件、网页，实现文件管理、网络爬虫等，非常实用，能立刻提升工作效率。
-        *   **适合人群**：办公室职员、运维人员，或任何想用程序解放双手的人。
-3.  **算法与面试**
-    *   **《Python算法详解》 - 张玲玲**
-    *   **《程序员面试金典》等**
-        *   **推荐理由**：国内作者写的，用Python讲解常见数据结构和算法，对准备面试很有帮助。
-### 四、 综合建议与电子资源
-*   **最佳学习路径建议**：
-    *   **第一步（入门）**：选择《Python编程：从入门到实践》或《笨办法学Python3》，**一定要跟着书敲代码**。
-    *   **第二步（进阶）**：在完成一些小项目后，开始阅读《流畅的Python》或《Effective Python》，提升内功。
-    *   **第三步（专精）**：根据你的职业方向（数据、Web、测试等），选择对应的领域书籍。
-*   **免费电子资源**：
-    *   **官方教程**：Python官网的教程是最好、最权威的入门资料之一。
-    *   **廖雪峰的Python教程**：中文，在线免费，讲解通俗易懂，非常适合入门。
-    *   **菜鸟教程**：适合快速查找某个语法点。
-**总结一下：**
-*   **如果你是纯新手，只想买一本**：**《Python编程：从入门到实践》** 是最稳妥、最全面的选择。
-*   **如果你已经入门，感到迷茫想提升**：**《流畅的Python》** 会为你打开新世界的大门。
-*   **如果你要做数据分析**：**《利用Python进行数据分析》** 是你的不二之选。
-希望这个推荐列表能帮助你找到最适合你的那本Python书！祝你学习愉快！</t>
+          <t>为你推荐几本不同层次和方向的Python书籍，你可以根据自己的需求选择：
+### 入门首选（零基础友好）
+**《Python编程：从入门到实践》（第2版）**
+- 作者：Eric Matthes
+- 特点：全球畅销入门书，项目驱动学习，包含基础语法和实际项目（数据可视化、Web应用、游戏开发）
+- 适合人群：完全零基础，喜欢动手实践的初学者
+### 经典全面（系统学习）
+**《Python核心编程》（第3版）**
+- 作者：Wesley Chun
+- 特点：内容全面深入，涵盖网络编程、GUI、数据库、Web开发等
+- 适合人群：想系统掌握Python各个应用领域的开发者
+### 进阶提升（写出优雅代码）
+**《流畅的Python》**
+- 作者：Luciano Ramalho
+- 特点：深入Python特性，讲解Pythonic编程风格和高级特性
+- 适合人群：已有基础，想写出更专业、高效Python代码的开发者
+### 实用工具书（数据分析方向）
+**《利用Python进行数据分析》（第2版）**
+- 作者：Wes McKinney（pandas库创始人）
+- 特点：专注数据科学工具链（pandas、NumPy、Jupyter等）
+- 适合人群：想做数据分析、数据科学的开发者
+### 面试准备（算法与面试）
+**《Python算法教程》**
+- 作者：Magnus Lie Hetland
+- 特点：用Python讲解算法，包含大量面试常见算法问题
+- 适合人群：准备技术面试或想提升算法能力的开发者
+### 选择建议：
+1. **完全新手** → 《Python编程：从入门到实践》
+2. **想全面掌握** → 《Python核心编程》 + 《流畅的Python》（分阶段学习）
+3. **数据分析方向** → 《利用Python进行数据分析》
+4. **已有基础想进阶** → 《流畅的Python》
+### 额外资源：
+- **免费在线教程**：官方文档（docs.python.org）、廖雪峰Python教程
+- **实战平台**：LeetCode（算法）、Kaggle（数据科学）
+你可以告诉我你的具体学习目标（如Web开发、数据分析、自动化等）和当前水平，我可以给出更针对性的建议！ 📚</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -614,14 +625,21 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1096</v>
+        <v>493</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>相似度得分 0.0761，低于阈值 0.5</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.07605995311034805</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
